--- a/output/cv_percetage.xlsx
+++ b/output/cv_percetage.xlsx
@@ -491,7 +491,7 @@
         <v>76.20210104768525</v>
       </c>
       <c r="H2" t="n">
-        <v>114.1080383293539</v>
+        <v>66.39574784913388</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         <v>80.81220356417687</v>
       </c>
       <c r="H3" t="n">
-        <v>44.04927489358822</v>
+        <v>42.42721463665282</v>
       </c>
     </row>
     <row r="4">
